--- a/data/trans_orig/P16A10-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A10-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21805</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>16737</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14715</t>
+          <t>14156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33585</t>
+          <t>33222</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>251205</t>
+          <t>251814</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264865</t>
+          <t>265020</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>243833</t>
+          <t>244101</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>256825</t>
+          <t>256649</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>500263</t>
+          <t>500626</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>519133</t>
+          <t>519692</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23923</t>
+          <t>23643</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47125</t>
+          <t>47119</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17363</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37367</t>
+          <t>37536</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45441</t>
+          <t>44314</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75326</t>
+          <t>76667</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>445950</t>
+          <t>445956</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>469152</t>
+          <t>469432</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>466582</t>
+          <t>466413</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>486586</t>
+          <t>486149</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>921698</t>
+          <t>920357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>951583</t>
+          <t>952710</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22938</t>
+          <t>22646</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>10788</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26833</t>
+          <t>27016</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21536</t>
+          <t>21541</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43601</t>
+          <t>43356</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295908</t>
+          <t>296200</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310762</t>
+          <t>310541</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308579</t>
+          <t>308396</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>325260</t>
+          <t>324624</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>610657</t>
+          <t>610902</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>632722</t>
+          <t>632717</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22943</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>14151</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31929</t>
+          <t>32350</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>26399</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48262</t>
+          <t>49412</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>335728</t>
+          <t>336422</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>349837</t>
+          <t>350667</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>339527</t>
+          <t>339106</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357737</t>
+          <t>357305</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>681865</t>
+          <t>680715</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>703472</t>
+          <t>703728</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24393</t>
+          <t>25725</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18558</t>
+          <t>18421</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17880</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37028</t>
+          <t>37989</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>178915</t>
+          <t>177583</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193386</t>
+          <t>193339</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>189110</t>
+          <t>189247</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202378</t>
+          <t>202567</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>373948</t>
+          <t>372987</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>393096</t>
+          <t>393475</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26765</t>
+          <t>26367</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11674</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29170</t>
+          <t>29938</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26863</t>
+          <t>25933</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50572</t>
+          <t>49440</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244046</t>
+          <t>244444</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259530</t>
+          <t>259352</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>248974</t>
+          <t>248206</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>266470</t>
+          <t>266402</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>498383</t>
+          <t>499515</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>522092</t>
+          <t>523022</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17634</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37821</t>
+          <t>37044</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21292</t>
+          <t>21580</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42480</t>
+          <t>43291</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43703</t>
+          <t>44299</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73510</t>
+          <t>73094</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>577206</t>
+          <t>577983</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>597393</t>
+          <t>597072</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>595739</t>
+          <t>594928</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>616927</t>
+          <t>616639</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1179736</t>
+          <t>1180152</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1209543</t>
+          <t>1208947</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30891</t>
+          <t>32081</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56082</t>
+          <t>55810</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32012</t>
+          <t>31474</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59999</t>
+          <t>58795</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70317</t>
+          <t>70075</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>106724</t>
+          <t>107380</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>686695</t>
+          <t>686967</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>711886</t>
+          <t>710696</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>723512</t>
+          <t>724716</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>751499</t>
+          <t>752037</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1419564</t>
+          <t>1418908</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1455971</t>
+          <t>1456213</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>151478</t>
+          <t>153538</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>205422</t>
+          <t>202598</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>154492</t>
+          <t>154493</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>204222</t>
+          <t>207824</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>319374</t>
+          <t>322063</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>391562</t>
+          <t>393925</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3070103</t>
+          <t>3072927</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3124047</t>
+          <t>3121987</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3174975</t>
+          <t>3171373</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3224705</t>
+          <t>3224704</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6263160</t>
+          <t>6260797</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6335348</t>
+          <t>6332659</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8118</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25264</t>
+          <t>25055</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>8787</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25893</t>
+          <t>25071</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20285</t>
+          <t>21046</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43701</t>
+          <t>44310</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265754</t>
+          <t>265963</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>282900</t>
+          <t>282858</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>258284</t>
+          <t>259106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275272</t>
+          <t>275390</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>531494</t>
+          <t>530885</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>554910</t>
+          <t>554149</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>12316</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30039</t>
+          <t>30436</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17933</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38046</t>
+          <t>38249</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60820</t>
+          <t>62000</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>475488</t>
+          <t>475091</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>494117</t>
+          <t>493211</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>483689</t>
+          <t>483486</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>503802</t>
+          <t>503605</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>966443</t>
+          <t>965263</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>992572</t>
+          <t>992765</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12318</t>
+          <t>13014</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30624</t>
+          <t>31934</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15069</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33068</t>
+          <t>33050</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31182</t>
+          <t>31354</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56775</t>
+          <t>56729</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>292492</t>
+          <t>291182</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310798</t>
+          <t>310102</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307952</t>
+          <t>307970</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>325951</t>
+          <t>327239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>607361</t>
+          <t>607407</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>632954</t>
+          <t>632782</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18269</t>
+          <t>18068</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39354</t>
+          <t>40149</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>12538</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29601</t>
+          <t>30299</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34222</t>
+          <t>35804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61816</t>
+          <t>61425</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>334628</t>
+          <t>333833</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355713</t>
+          <t>355914</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>358373</t>
+          <t>357675</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>375957</t>
+          <t>375436</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>700140</t>
+          <t>700531</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>727734</t>
+          <t>726152</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21338</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>7670</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22193</t>
+          <t>22243</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>17984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38545</t>
+          <t>38664</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>191280</t>
+          <t>189822</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205783</t>
+          <t>204870</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197398</t>
+          <t>197348</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>212031</t>
+          <t>211921</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>393664</t>
+          <t>393545</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>414717</t>
+          <t>414225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>27357</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11557</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29045</t>
+          <t>29983</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26480</t>
+          <t>27024</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49230</t>
+          <t>49832</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246938</t>
+          <t>246624</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263600</t>
+          <t>263447</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>250095</t>
+          <t>249157</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>267583</t>
+          <t>267711</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>503891</t>
+          <t>503289</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>526641</t>
+          <t>526097</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30898</t>
+          <t>31858</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56562</t>
+          <t>58114</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16127</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36716</t>
+          <t>35366</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53388</t>
+          <t>51282</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86395</t>
+          <t>84949</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>606226</t>
+          <t>604674</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>631890</t>
+          <t>630930</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>657137</t>
+          <t>658487</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>677726</t>
+          <t>677625</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1270246</t>
+          <t>1271692</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1303253</t>
+          <t>1305359</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15118</t>
+          <t>15478</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36705</t>
+          <t>36109</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20179</t>
+          <t>19681</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42460</t>
+          <t>43370</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40701</t>
+          <t>40300</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73191</t>
+          <t>70691</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>740267</t>
+          <t>740863</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>761854</t>
+          <t>761494</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>779219</t>
+          <t>778309</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>801500</t>
+          <t>801998</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1525460</t>
+          <t>1527960</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1557950</t>
+          <t>1558351</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>153180</t>
+          <t>155255</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>207758</t>
+          <t>211198</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,82 +6815,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>170460</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>146419</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>199323</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>350949</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>312413</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>388024</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>4,48%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>6,07%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>170460</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>144719</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>196865</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>350949</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>314112</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>386473</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3212245</t>
+          <t>3208805</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3266823</t>
+          <t>3264748</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,82 +6928,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>95,46%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3378710</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>3349847</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3402751</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>95,2%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>94,38%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>95,87%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>6167</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6618224</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6581149</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6656760</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>94,96%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>94,43%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>95,52%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>3130</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3378710</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>3352305</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3404451</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>95,2%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>94,45%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>95,92%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>6167</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6618224</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6582700</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6655061</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>94,96%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>94,45%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21489</t>
+          <t>20655</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>21972</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17175</t>
+          <t>17151</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37267</t>
+          <t>38015</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>272272</t>
+          <t>273106</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286563</t>
+          <t>286625</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265606</t>
+          <t>266731</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281612</t>
+          <t>282071</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>545197</t>
+          <t>544449</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>565289</t>
+          <t>565313</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25163</t>
+          <t>25195</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47460</t>
+          <t>48143</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19348</t>
+          <t>19641</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40447</t>
+          <t>39840</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50048</t>
+          <t>50164</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81403</t>
+          <t>82634</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>455115</t>
+          <t>454432</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>477412</t>
+          <t>477380</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>482637</t>
+          <t>483244</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>503736</t>
+          <t>503443</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>944256</t>
+          <t>943025</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>975611</t>
+          <t>975495</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>26548</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18505</t>
+          <t>18061</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39234</t>
+          <t>39947</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>292538</t>
+          <t>292017</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307169</t>
+          <t>307030</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>317814</t>
+          <t>317359</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332242</t>
+          <t>332000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615640</t>
+          <t>614927</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>636369</t>
+          <t>636813</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16174</t>
+          <t>16970</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35824</t>
+          <t>34846</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28672</t>
+          <t>28790</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57067</t>
+          <t>56691</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50099</t>
+          <t>50352</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84245</t>
+          <t>83845</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>334140</t>
+          <t>335118</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>353790</t>
+          <t>352994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>330216</t>
+          <t>330592</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>358611</t>
+          <t>358493</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>673002</t>
+          <t>673402</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>707148</t>
+          <t>706895</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22169</t>
+          <t>20095</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17074</t>
+          <t>17646</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32446</t>
+          <t>32540</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>189052</t>
+          <t>191126</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204155</t>
+          <t>204449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201513</t>
+          <t>200941</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214365</t>
+          <t>214023</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>397362</t>
+          <t>397268</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>414656</t>
+          <t>415551</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21253</t>
+          <t>22534</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12932</t>
+          <t>12864</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32229</t>
+          <t>31352</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22906</t>
+          <t>22719</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47809</t>
+          <t>44720</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>241870</t>
+          <t>240589</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256605</t>
+          <t>255916</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>240886</t>
+          <t>241763</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>260183</t>
+          <t>260251</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>488429</t>
+          <t>491518</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>513332</t>
+          <t>513519</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24301</t>
+          <t>25289</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47993</t>
+          <t>49545</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,47 +9452,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>7,55%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>25547</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>15830</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>37878</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>3,7%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>7,31%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>25547</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>16599</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>38182</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46060</t>
+          <t>46233</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79246</t>
+          <t>77624</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>608565</t>
+          <t>607013</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>632257</t>
+          <t>631269</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,47 +9565,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>665747</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>653416</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>675464</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>96,3%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>665747</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>653112</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>674695</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>96,3%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1268606</t>
+          <t>1270228</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1301792</t>
+          <t>1301619</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38369</t>
+          <t>37982</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>67974</t>
+          <t>66049</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30697</t>
+          <t>31268</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58031</t>
+          <t>56519</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>77504</t>
+          <t>74926</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>116949</t>
+          <t>115639</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>710609</t>
+          <t>712534</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>740214</t>
+          <t>740601</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>768136</t>
+          <t>769648</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>795470</t>
+          <t>794899</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1487801</t>
+          <t>1489111</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1527246</t>
+          <t>1529824</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>173541</t>
+          <t>174520</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>230261</t>
+          <t>230470</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>163842</t>
+          <t>163587</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>219186</t>
+          <t>222624</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>353330</t>
+          <t>357015</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>434981</t>
+          <t>434160</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3164089</t>
+          <t>3163880</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3220809</t>
+          <t>3219830</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3325356</t>
+          <t>3321918</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3380700</t>
+          <t>3380955</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6503911</t>
+          <t>6504732</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6585562</t>
+          <t>6581877</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>11015</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25282</t>
+          <t>25453</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18748</t>
+          <t>19633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19892</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39039</t>
+          <t>39094</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>286161</t>
+          <t>285990</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>300765</t>
+          <t>300428</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270887</t>
+          <t>270002</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282461</t>
+          <t>282463</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>562038</t>
+          <t>561983</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>581185</t>
+          <t>580634</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>21395</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43995</t>
+          <t>44465</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15946</t>
+          <t>17467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32080</t>
+          <t>32407</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43736</t>
+          <t>43786</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72810</t>
+          <t>71043</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>473398</t>
+          <t>472928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>494932</t>
+          <t>495998</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>481645</t>
+          <t>481318</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497779</t>
+          <t>496258</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>958308</t>
+          <t>960075</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>987382</t>
+          <t>987332</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13432</t>
+          <t>13835</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27966</t>
+          <t>27723</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17935</t>
+          <t>17977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33051</t>
+          <t>32401</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34247</t>
+          <t>34893</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54132</t>
+          <t>54974</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288084</t>
+          <t>288327</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302618</t>
+          <t>302215</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>316077</t>
+          <t>316727</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>331193</t>
+          <t>331151</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>611046</t>
+          <t>610204</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>630931</t>
+          <t>630285</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28644</t>
+          <t>27022</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>10994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29955</t>
+          <t>28615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25829</t>
+          <t>26264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51367</t>
+          <t>50654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283913</t>
+          <t>285535</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299164</t>
+          <t>299841</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>445763</t>
+          <t>447103</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>465034</t>
+          <t>464724</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>736907</t>
+          <t>737620</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>762445</t>
+          <t>762010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13246</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20721</t>
+          <t>21071</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168737</t>
+          <t>168464</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175551</t>
+          <t>175509</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195410</t>
+          <t>195530</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202624</t>
+          <t>203054</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>366677</t>
+          <t>366327</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>376638</t>
+          <t>376627</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22754</t>
+          <t>23578</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>19495</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23934</t>
+          <t>23544</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37897</t>
+          <t>39079</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246882</t>
+          <t>246058</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257939</t>
+          <t>257747</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237644</t>
+          <t>237561</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247116</t>
+          <t>247499</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>488795</t>
+          <t>487613</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>502758</t>
+          <t>503148</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24080</t>
+          <t>24997</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45664</t>
+          <t>45844</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17415</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>51633</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42166</t>
+          <t>42702</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88595</t>
+          <t>90320</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>578615</t>
+          <t>578435</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>600199</t>
+          <t>599282</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>797703</t>
+          <t>797632</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>831850</t>
+          <t>832401</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1384949</t>
+          <t>1383224</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1431378</t>
+          <t>1430842</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>16955</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62652</t>
+          <t>61690</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>33421</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51400</t>
+          <t>52136</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>50925</t>
+          <t>50217</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>104620</t>
+          <t>103461</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>866068</t>
+          <t>867030</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>910920</t>
+          <t>911765</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>662840</t>
+          <t>662104</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>680968</t>
+          <t>680819</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1538340</t>
+          <t>1539499</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1592035</t>
+          <t>1592743</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>141855</t>
+          <t>135483</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>213766</t>
+          <t>213993</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>144087</t>
+          <t>146292</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>202394</t>
+          <t>203907</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>317171</t>
+          <t>320204</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>406526</t>
+          <t>408796</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3245054</t>
+          <t>3244827</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3316965</t>
+          <t>3323337</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3455027</t>
+          <t>3453514</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3513334</t>
+          <t>3511129</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6709715</t>
+          <t>6707445</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6799070</t>
+          <t>6796037</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A10-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A10-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>8119</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21196</t>
+          <t>22143</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16737</t>
+          <t>15984</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14156</t>
+          <t>14341</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33222</t>
+          <t>32826</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>251814</t>
+          <t>250867</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>265020</t>
+          <t>264891</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>244101</t>
+          <t>244854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>256649</t>
+          <t>256989</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>500626</t>
+          <t>501022</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>519692</t>
+          <t>519507</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23643</t>
+          <t>22138</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47119</t>
+          <t>44640</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>17461</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37536</t>
+          <t>38044</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44314</t>
+          <t>46523</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76667</t>
+          <t>76192</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>445956</t>
+          <t>448435</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>469432</t>
+          <t>470937</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>466413</t>
+          <t>465905</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>486149</t>
+          <t>486488</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>920357</t>
+          <t>920832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952710</t>
+          <t>950501</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22646</t>
+          <t>22167</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>10545</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27016</t>
+          <t>25763</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21541</t>
+          <t>21628</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43356</t>
+          <t>43384</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296200</t>
+          <t>296679</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310541</t>
+          <t>310691</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308396</t>
+          <t>309649</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324624</t>
+          <t>324867</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>610902</t>
+          <t>610874</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>632717</t>
+          <t>632630</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>8899</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>23034</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14151</t>
+          <t>13530</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32350</t>
+          <t>30512</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26399</t>
+          <t>26841</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49412</t>
+          <t>48501</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>336422</t>
+          <t>335637</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>350667</t>
+          <t>349772</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>339106</t>
+          <t>340944</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357305</t>
+          <t>357926</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>680715</t>
+          <t>681626</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>703728</t>
+          <t>703286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9969</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25725</t>
+          <t>24927</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18148</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>18325</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37989</t>
+          <t>38536</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177583</t>
+          <t>178381</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193339</t>
+          <t>193670</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>189247</t>
+          <t>189520</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202567</t>
+          <t>202192</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>372987</t>
+          <t>372440</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>393475</t>
+          <t>392651</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26367</t>
+          <t>26343</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11742</t>
+          <t>11659</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29938</t>
+          <t>30563</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25933</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49440</t>
+          <t>50429</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244444</t>
+          <t>244468</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259352</t>
+          <t>260634</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>248206</t>
+          <t>247581</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>266402</t>
+          <t>266485</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>499515</t>
+          <t>498526</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>523022</t>
+          <t>522210</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17955</t>
+          <t>17499</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37044</t>
+          <t>36590</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21580</t>
+          <t>21117</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43291</t>
+          <t>43191</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44299</t>
+          <t>43423</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73094</t>
+          <t>72667</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>577983</t>
+          <t>578437</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>597072</t>
+          <t>597528</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>594928</t>
+          <t>595028</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>616639</t>
+          <t>617102</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1180152</t>
+          <t>1180579</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1208947</t>
+          <t>1209823</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32081</t>
+          <t>31579</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55810</t>
+          <t>56856</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31474</t>
+          <t>33371</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58795</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70075</t>
+          <t>71778</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>107380</t>
+          <t>107619</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>686967</t>
+          <t>685921</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>710696</t>
+          <t>711198</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>724716</t>
+          <t>724078</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>752037</t>
+          <t>750140</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1418908</t>
+          <t>1418669</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1456213</t>
+          <t>1454510</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>153538</t>
+          <t>153862</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>202598</t>
+          <t>202443</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>154493</t>
+          <t>155486</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>207824</t>
+          <t>205837</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>322063</t>
+          <t>319303</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>393925</t>
+          <t>393067</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3072927</t>
+          <t>3073082</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3121987</t>
+          <t>3121663</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3171373</t>
+          <t>3173360</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3224704</t>
+          <t>3223711</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6260797</t>
+          <t>6261655</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6332659</t>
+          <t>6335419</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25055</t>
+          <t>23999</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25071</t>
+          <t>25199</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21046</t>
+          <t>20530</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44310</t>
+          <t>42927</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265963</t>
+          <t>267019</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>282858</t>
+          <t>283242</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259106</t>
+          <t>258978</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275390</t>
+          <t>275125</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>530885</t>
+          <t>532268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>554149</t>
+          <t>554665</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12316</t>
+          <t>11769</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30436</t>
+          <t>30826</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18130</t>
+          <t>18038</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38249</t>
+          <t>38537</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34498</t>
+          <t>33353</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62000</t>
+          <t>59967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>475091</t>
+          <t>474701</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>493211</t>
+          <t>493758</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>483486</t>
+          <t>483198</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>503605</t>
+          <t>503697</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>965263</t>
+          <t>967296</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>992765</t>
+          <t>993910</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>12446</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31934</t>
+          <t>30893</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>14891</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33050</t>
+          <t>33616</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31354</t>
+          <t>30599</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56729</t>
+          <t>57412</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>291182</t>
+          <t>292223</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310102</t>
+          <t>310670</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307970</t>
+          <t>307404</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327239</t>
+          <t>326129</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>607407</t>
+          <t>606724</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>632782</t>
+          <t>633537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>18634</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40149</t>
+          <t>39777</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12538</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30299</t>
+          <t>29192</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35804</t>
+          <t>33498</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61425</t>
+          <t>59979</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>333833</t>
+          <t>334205</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355914</t>
+          <t>355348</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>357675</t>
+          <t>358782</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>375436</t>
+          <t>375890</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>700531</t>
+          <t>701977</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>726152</t>
+          <t>728458</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>22126</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7670</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22243</t>
+          <t>22551</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17984</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38664</t>
+          <t>37698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>189822</t>
+          <t>190492</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204870</t>
+          <t>205809</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197348</t>
+          <t>197040</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>211921</t>
+          <t>212365</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>393545</t>
+          <t>394511</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>414225</t>
+          <t>414487</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10534</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27357</t>
+          <t>26973</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11429</t>
+          <t>11581</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29983</t>
+          <t>29357</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>26766</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49832</t>
+          <t>48677</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246624</t>
+          <t>247008</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263447</t>
+          <t>262977</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>249157</t>
+          <t>249783</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>267711</t>
+          <t>267559</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>503289</t>
+          <t>504444</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>526097</t>
+          <t>526355</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31858</t>
+          <t>31819</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58114</t>
+          <t>57348</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16228</t>
+          <t>15849</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35366</t>
+          <t>35983</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51282</t>
+          <t>53452</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84949</t>
+          <t>85844</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>604674</t>
+          <t>605440</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>630930</t>
+          <t>630969</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>658487</t>
+          <t>657870</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>677625</t>
+          <t>678004</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1271692</t>
+          <t>1270797</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1305359</t>
+          <t>1303189</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15478</t>
+          <t>15792</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36109</t>
+          <t>35885</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19681</t>
+          <t>19948</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43370</t>
+          <t>42600</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40300</t>
+          <t>39352</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70691</t>
+          <t>70212</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>740863</t>
+          <t>741087</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>761494</t>
+          <t>761180</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>778309</t>
+          <t>779079</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>801998</t>
+          <t>801731</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1527960</t>
+          <t>1528439</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1558351</t>
+          <t>1559299</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>155255</t>
+          <t>154266</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>211198</t>
+          <t>214229</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>146419</t>
+          <t>145695</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>199323</t>
+          <t>196463</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>312413</t>
+          <t>314378</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>388024</t>
+          <t>386052</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3208805</t>
+          <t>3205774</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3264748</t>
+          <t>3265737</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3349847</t>
+          <t>3352707</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3402751</t>
+          <t>3403475</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6581149</t>
+          <t>6583121</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6656760</t>
+          <t>6654795</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20655</t>
+          <t>21481</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21972</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17151</t>
+          <t>17920</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38015</t>
+          <t>38599</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273106</t>
+          <t>272280</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286625</t>
+          <t>286703</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266731</t>
+          <t>266352</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282071</t>
+          <t>282084</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>544449</t>
+          <t>543865</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>565313</t>
+          <t>564544</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25195</t>
+          <t>24739</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48143</t>
+          <t>48461</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19641</t>
+          <t>20104</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39840</t>
+          <t>41543</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50164</t>
+          <t>49084</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82634</t>
+          <t>80226</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>454432</t>
+          <t>454114</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>477380</t>
+          <t>477836</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>483244</t>
+          <t>481541</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>503443</t>
+          <t>502980</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>943025</t>
+          <t>945433</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>975495</t>
+          <t>976575</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>26434</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>17910</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>18429</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39947</t>
+          <t>38922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>292017</t>
+          <t>292131</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307030</t>
+          <t>308051</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>317359</t>
+          <t>318399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332000</t>
+          <t>332182</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>614927</t>
+          <t>615952</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>636813</t>
+          <t>636445</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16970</t>
+          <t>16956</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34846</t>
+          <t>35102</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28790</t>
+          <t>28903</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56691</t>
+          <t>57218</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50352</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83845</t>
+          <t>84332</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>335118</t>
+          <t>334862</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>352994</t>
+          <t>353008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>330592</t>
+          <t>330065</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>358493</t>
+          <t>358380</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>673402</t>
+          <t>672915</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>706895</t>
+          <t>705953</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20095</t>
+          <t>21506</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17646</t>
+          <t>17316</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14257</t>
+          <t>13598</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32540</t>
+          <t>31663</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>191126</t>
+          <t>189715</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204449</t>
+          <t>203810</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200941</t>
+          <t>201271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214023</t>
+          <t>214123</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>397268</t>
+          <t>398145</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>415551</t>
+          <t>416210</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22534</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>12266</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31352</t>
+          <t>33282</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22719</t>
+          <t>22973</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44720</t>
+          <t>46842</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>240589</t>
+          <t>242166</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>255916</t>
+          <t>255762</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>241763</t>
+          <t>239833</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>260251</t>
+          <t>260849</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>491518</t>
+          <t>489396</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>513519</t>
+          <t>513265</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25289</t>
+          <t>24497</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49545</t>
+          <t>48974</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15830</t>
+          <t>15632</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37878</t>
+          <t>37337</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46233</t>
+          <t>46912</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77624</t>
+          <t>77785</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>607013</t>
+          <t>607584</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>631269</t>
+          <t>632061</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>653416</t>
+          <t>653957</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>675464</t>
+          <t>675662</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1270228</t>
+          <t>1270067</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1301619</t>
+          <t>1300940</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37982</t>
+          <t>39867</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66049</t>
+          <t>68511</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31268</t>
+          <t>30866</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56519</t>
+          <t>58217</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74926</t>
+          <t>76623</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>115639</t>
+          <t>115722</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>712534</t>
+          <t>710072</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>740601</t>
+          <t>738716</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>769648</t>
+          <t>767950</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>794899</t>
+          <t>795301</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1489111</t>
+          <t>1489028</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1529824</t>
+          <t>1528127</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>174520</t>
+          <t>176028</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>230470</t>
+          <t>232086</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>163587</t>
+          <t>163437</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>222624</t>
+          <t>222554</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>357015</t>
+          <t>358205</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>434160</t>
+          <t>438331</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3163880</t>
+          <t>3162264</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3219830</t>
+          <t>3218322</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3321918</t>
+          <t>3321988</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3380955</t>
+          <t>3381105</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6504732</t>
+          <t>6500561</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6581877</t>
+          <t>6580687</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16736</t>
+          <t>18277</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25453</t>
+          <t>26592</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>11104</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19633</t>
+          <t>17136</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>28236</t>
+          <t>29381</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>21467</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39094</t>
+          <t>38975</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>294707</t>
+          <t>300568</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285990</t>
+          <t>292253</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>300428</t>
+          <t>306742</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>278135</t>
+          <t>304957</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270002</t>
+          <t>298925</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282463</t>
+          <t>309218</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>572841</t>
+          <t>605525</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561983</t>
+          <t>595931</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>580634</t>
+          <t>613439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,17 +11040,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32144</t>
+          <t>32880</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21395</t>
+          <t>22094</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44465</t>
+          <t>45420</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23420</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17467</t>
+          <t>17243</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32407</t>
+          <t>32966</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>55564</t>
+          <t>57269</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43786</t>
+          <t>43663</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71043</t>
+          <t>71362</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -11153,17 +11153,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>485249</t>
+          <t>496780</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472928</t>
+          <t>484240</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495998</t>
+          <t>507566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>490305</t>
+          <t>520823</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>481318</t>
+          <t>512247</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496258</t>
+          <t>527970</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>975554</t>
+          <t>1017604</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>960075</t>
+          <t>1003511</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>987332</t>
+          <t>1031210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19663</t>
+          <t>19431</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>13153</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27723</t>
+          <t>27853</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24689</t>
+          <t>24857</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17977</t>
+          <t>17457</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32401</t>
+          <t>32825</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>44352</t>
+          <t>44288</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34893</t>
+          <t>34860</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54974</t>
+          <t>55371</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>296387</t>
+          <t>296562</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288327</t>
+          <t>288140</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302215</t>
+          <t>302840</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>324439</t>
+          <t>331524</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>316727</t>
+          <t>323556</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>331151</t>
+          <t>338924</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>620826</t>
+          <t>628087</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>610204</t>
+          <t>617004</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>630285</t>
+          <t>637515</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>21776</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12716</t>
+          <t>14963</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27022</t>
+          <t>31433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>19940</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>13686</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28615</t>
+          <t>30881</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>37858</t>
+          <t>41717</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26264</t>
+          <t>31730</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50654</t>
+          <t>56690</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>293334</t>
+          <t>351369</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>285535</t>
+          <t>341712</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299841</t>
+          <t>358182</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>457083</t>
+          <t>402021</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>447103</t>
+          <t>391080</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>464724</t>
+          <t>408275</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>750416</t>
+          <t>753390</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>737620</t>
+          <t>738417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>762010</t>
+          <t>763377</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9129</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13595</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>15240</t>
+          <t>16178</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10771</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>22878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>172631</t>
+          <t>198888</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168464</t>
+          <t>194399</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175509</t>
+          <t>202004</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>199527</t>
+          <t>217814</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195530</t>
+          <t>213620</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203054</t>
+          <t>221015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>372158</t>
+          <t>416701</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>366327</t>
+          <t>410001</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>376627</t>
+          <t>421441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16569</t>
+          <t>16330</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11889</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23578</t>
+          <t>23024</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13825</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19495</t>
+          <t>20043</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>30394</t>
+          <t>30768</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23544</t>
+          <t>23724</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39079</t>
+          <t>38432</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>253067</t>
+          <t>254377</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246058</t>
+          <t>247683</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257747</t>
+          <t>259063</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>243231</t>
+          <t>249312</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237561</t>
+          <t>243707</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247499</t>
+          <t>253556</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>496298</t>
+          <t>503689</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>487613</t>
+          <t>496025</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>503148</t>
+          <t>510733</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>34248</t>
+          <t>41945</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24997</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45844</t>
+          <t>55646</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>36343</t>
+          <t>46665</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>36344</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51633</t>
+          <t>60110</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>70591</t>
+          <t>88609</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42702</t>
+          <t>72733</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90320</t>
+          <t>106287</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>590031</t>
+          <t>677742</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>578435</t>
+          <t>664041</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>599282</t>
+          <t>689247</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>725392</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>797632</t>
+          <t>711947</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>832401</t>
+          <t>735713</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1402953</t>
+          <t>1403135</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1383224</t>
+          <t>1385457</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1430842</t>
+          <t>1419011</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>41860</t>
+          <t>46817</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16955</t>
+          <t>36891</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61690</t>
+          <t>60311</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>41989</t>
+          <t>48051</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33421</t>
+          <t>38045</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52136</t>
+          <t>58979</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>83849</t>
+          <t>94868</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>50217</t>
+          <t>81681</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>103461</t>
+          <t>112646</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>886860</t>
+          <t>751255</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>867030</t>
+          <t>737761</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>911765</t>
+          <t>761181</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>672251</t>
+          <t>781243</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>662104</t>
+          <t>770315</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>680819</t>
+          <t>791249</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1559111</t>
+          <t>1532498</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1539499</t>
+          <t>1514720</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1592743</t>
+          <t>1545685</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714240</t>
+          <t>829294</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714240</t>
+          <t>829294</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714240</t>
+          <t>829294</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1642960</t>
+          <t>1627366</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1642960</t>
+          <t>1627366</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1642960</t>
+          <t>1627366</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>186554</t>
+          <t>204233</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>135483</t>
+          <t>180299</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>213993</t>
+          <t>230228</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>179530</t>
+          <t>198846</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>146292</t>
+          <t>179190</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>203907</t>
+          <t>222350</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>366084</t>
+          <t>403079</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>320204</t>
+          <t>370759</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>408796</t>
+          <t>439152</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3272266</t>
+          <t>3327542</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3244827</t>
+          <t>3301547</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3323337</t>
+          <t>3351476</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3477891</t>
+          <t>3533087</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3453514</t>
+          <t>3509583</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3511129</t>
+          <t>3552743</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6750157</t>
+          <t>6860628</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6707445</t>
+          <t>6824555</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6796037</t>
+          <t>6892948</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3657421</t>
+          <t>3731933</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3657421</t>
+          <t>3731933</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3657421</t>
+          <t>3731933</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7116241</t>
+          <t>7263707</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7116241</t>
+          <t>7263707</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7116241</t>
+          <t>7263707</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
